--- a/samples/eet/03_bad_formats.xlsx
+++ b/samples/eet/03_bad_formats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,12 +509,172 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>20190_Financial_Instrument_Sustainable_Investment_EU_Taxonomy_Art_8</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>20200_Financial_Instrument_Sustainable_Investment_Environmental_Not_EU_Taxonomy_Art_8</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>20210_Financial_Instrument_Sustainable_Investment_Social_Objective_Art_8</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>20220_Financial_Instrument_Minimum_Sustainable_Investment_With_Environmental_Objective_Art_9</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>20230_Financial_Instrument_Environmentally_Sustainable_Investment_EU_Taxonomy_Art_9</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>20240_Financial_Instrument_Environmentally_Sustainable_Investment_Not_EU_Taxonomy_Art_9</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>20250_Financial_Instrument_Minimum_Sustainable_Investment_Social_Objective_Art_9</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>30000_PAI_Snapshot_Frequency</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>30010_PAI_Reference_Date</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>30030_GHG_Emissions_Scope_1_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>30070_GHG_Emissions_Scope_2_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>30110_GHG_Emissions_Scope_3_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>30150_GHG_Emissions_Total_Scope12_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>30190_GHG_Emissions_Total_Scope123_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>30230_Carbon_Footprint_Scope12_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>30270_Carbon_Footprint_Scope123_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>30310_GHG_Intensity_Of_Investee_Companies_Scope12_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>30350_GHG_Intensity_Of_Investee_Companies_Scope123_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>30390_Exposure_To_Companies_Active_In_The_Fossil_Fuel_Sector_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>30430_Share_Energy_Consumption_From_Non-Renewable_Sources_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>30470_Share_Energy_Production_From_Non-Renewable_Sources_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>30510_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_A_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>30550_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_B_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>30590_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_C_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>30630_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_D_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>30670_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_E_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>30710_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_F_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>30750_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_G_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>30790_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_H_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>30830_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_M_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>30870_Activities_Negatively_Affecting_Biodiversity-sensitive_Areas_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>30910_Water_Emissions_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>30950_Hazardous_Waste_Ratio_Considered_In_The_Investment_Strategy</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>30990_Share_Of_Companies_Involved_In_Violation_Of_UN_Global_Compact_Principles_And_OECD_Guidelines_For_Multinational_Enterprises_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
     </row>
@@ -576,7 +736,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -603,6 +763,42 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/eet/03_bad_formats.xlsx
+++ b/samples/eet/03_bad_formats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:BB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,180 +499,190 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>20120_Financial_Instrument_Link_To_PCDFP_For_MOP</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>20130_Financial_Instrument_Production_Date_PCDFP</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>20170_Financial_Instrument_Sustainable_Investments_Art_8</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>20180_Financial_Instrument_Products_Minimal_Proportion_Of_Sustainable_Investments_Art_8</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>20190_Financial_Instrument_Sustainable_Investment_EU_Taxonomy_Art_8</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>20200_Financial_Instrument_Sustainable_Investment_Environmental_Not_EU_Taxonomy_Art_8</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>20210_Financial_Instrument_Sustainable_Investment_Social_Objective_Art_8</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>20220_Financial_Instrument_Minimum_Sustainable_Investment_With_Environmental_Objective_Art_9</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>20230_Financial_Instrument_Environmentally_Sustainable_Investment_EU_Taxonomy_Art_9</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>20240_Financial_Instrument_Environmentally_Sustainable_Investment_Not_EU_Taxonomy_Art_9</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>20250_Financial_Instrument_Minimum_Sustainable_Investment_Social_Objective_Art_9</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>30000_PAI_Snapshot_Frequency</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>30010_PAI_Reference_Date</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>30030_GHG_Emissions_Scope_1_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>30070_GHG_Emissions_Scope_2_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>30110_GHG_Emissions_Scope_3_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>30150_GHG_Emissions_Total_Scope12_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>30190_GHG_Emissions_Total_Scope123_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>30230_Carbon_Footprint_Scope12_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>30270_Carbon_Footprint_Scope123_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>30310_GHG_Intensity_Of_Investee_Companies_Scope12_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>30350_GHG_Intensity_Of_Investee_Companies_Scope123_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>30390_Exposure_To_Companies_Active_In_The_Fossil_Fuel_Sector_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>30430_Share_Energy_Consumption_From_Non-Renewable_Sources_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>30470_Share_Energy_Production_From_Non-Renewable_Sources_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>30510_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_A_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>30550_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_B_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>30590_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_C_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>30630_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_D_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>30670_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_E_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>30710_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_F_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>30750_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_G_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>30790_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_H_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>30830_Energy_Consumption_Intensity_Per_High_Impact_Climate_Sector_NACE_M_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>30870_Activities_Negatively_Affecting_Biodiversity-sensitive_Areas_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>30910_Water_Emissions_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>30950_Hazardous_Waste_Ratio_Considered_In_The_Investment_Strategy</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>30990_Share_Of_Companies_Involved_In_Violation_Of_UN_Global_Compact_Principles_And_OECD_Guidelines_For_Multinational_Enterprises_Considered_In_The_Investment_Strategy</t>
         </is>
@@ -753,23 +763,31 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>https://findatex.example/pre-contractual/LU0001234567/EN.pdf</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
@@ -799,6 +817,8 @@
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
